--- a/artfynd/A 8216-2023 artfynd.xlsx
+++ b/artfynd/A 8216-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8216-2023 artfynd.xlsx
+++ b/artfynd/A 8216-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63102849</v>
+        <v>95861575</v>
       </c>
       <c r="B2" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Enlunda, Färingsö, Upl</t>
+          <t>Ekeby Gårds väg, Ekerö, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>657267.9450298361</v>
+        <v>657156</v>
       </c>
       <c r="R2" t="n">
-        <v>6577512.786612472</v>
+        <v>6577526</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-11-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-11-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hanna Nilsson</t>
+          <t>Tommy Jonestrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hanna Nilsson, Petter Andersson</t>
+          <t>Tommy Jonestrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,12 +780,7 @@
         <v>63102851</v>
       </c>
       <c r="B3" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>657256.1085185481</v>
+        <v>657256</v>
       </c>
       <c r="R3" t="n">
-        <v>6577538.877651496</v>
+        <v>6577539</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +845,9 @@
           <t>2016-11-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-11-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63102852</v>
+        <v>63102849</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>657253.0019719584</v>
+        <v>657268</v>
       </c>
       <c r="R4" t="n">
-        <v>6577552.039767824</v>
+        <v>6577513</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +942,9 @@
           <t>2016-11-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-11-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,12 +974,7 @@
         <v>63102850</v>
       </c>
       <c r="B5" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>657264.753728416</v>
+        <v>657265</v>
       </c>
       <c r="R5" t="n">
-        <v>6577527.990079138</v>
+        <v>6577528</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1039,9 @@
           <t>2016-11-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-11-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63102856</v>
+        <v>63102853</v>
       </c>
       <c r="B6" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>657304.0535506024</v>
+        <v>657270</v>
       </c>
       <c r="R6" t="n">
-        <v>6577531.154512618</v>
+        <v>6577555</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1136,9 @@
           <t>2016-11-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-11-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>63102853</v>
+        <v>63102856</v>
       </c>
       <c r="B7" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>657269.7871773213</v>
+        <v>657304</v>
       </c>
       <c r="R7" t="n">
-        <v>6577554.780983978</v>
+        <v>6577531</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1233,9 @@
           <t>2016-11-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2016-11-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95861575</v>
+        <v>63102857</v>
       </c>
       <c r="B8" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,42 +1273,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6031</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ekeby Gårds väg, Ekerö, Upl</t>
+          <t>Enlunda, Färingsö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>657155.2484027779</v>
+        <v>657286</v>
       </c>
       <c r="R8" t="n">
-        <v>6577526.003996371</v>
+        <v>6577531</v>
       </c>
       <c r="S8" t="n">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,22 +1327,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-11-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-11-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,79 +1347,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tommy Jonestrand</t>
+          <t>Hanna Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tommy Jonestrand</t>
+          <t>Hanna Nilsson, Petter Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95861565</v>
+        <v>63102852</v>
       </c>
       <c r="B9" t="n">
-        <v>90126</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>232138</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Ryman</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Byggmästarens väg 11, Ekerö, Upl</t>
+          <t>Enlunda, Färingsö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>657264.5328850473</v>
+        <v>657253</v>
       </c>
       <c r="R9" t="n">
-        <v>6577496.28669191</v>
+        <v>6577552</v>
       </c>
       <c r="S9" t="n">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,22 +1424,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-11-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-11-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,15 +1444,126 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson, Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>95861565</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Byggmästarens väg 11, Ekerö, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>657265</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6577496</v>
+      </c>
+      <c r="S10" t="n">
+        <v>96</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Tommy Jonestrand</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Tommy Jonestrand</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
